--- a/outputs/淹没分析结果_西茶坞村_24h10a.xlsx
+++ b/outputs/淹没分析结果_西茶坞村_24h10a.xlsx
@@ -787,7 +787,11 @@
       <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>E:\水科院\flood_workflow_app\outputs\校正后河道_西茶坞村_24h10a.geojson</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>村庄/小区</t>
@@ -16144,7 +16148,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1092.40081750151</v>
+        <v>1098.041325436782</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16173,30 +16177,30 @@
         <v>654.7603822322152</v>
       </c>
       <c r="L4" t="n">
-        <v>67.05399999991897</v>
+        <v>41.63212215936028</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>汇总表路-河中-村庄/小区-河中坐标锚定</t>
+          <t>汇总表路-河中-村庄/小区-河中坐标锚定-避让建筑(clearance=2m)</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>352.287</v>
+        <v>371.9072115185528</v>
       </c>
       <c r="O4" t="n">
-        <v>419.341</v>
+        <v>413.5393336778993</v>
       </c>
       <c r="P4" t="n">
         <v>401.993</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>路</t>
+          <t>建筑前缘</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>村庄/小区</t>
+          <t>建筑前缘</t>
         </is>
       </c>
       <c r="S4" t="n">
